--- a/data/daily/2026-08/2026-08-28.xlsx
+++ b/data/daily/2026-08/2026-08-28.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,92 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,27 +1450,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,24 +1503,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,154 +1528,129 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2941,7 +2941,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/11839566</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,27 +2984,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>45,800원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11839566</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
+          <t>29,900원</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
           <t>45,800원</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>29,900원</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -4054,7 +4054,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4062,27 +4062,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000283&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/zIbSOpTi3yHSeYULrLdY600000283_00_01zIbSOpTi3yHSeYULrLdY.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
     </row>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4147,19 +4147,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
+          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4217,19 +4217,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624078&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/LCCefMiAcRv8JhM7m90p913624078_00_00LCCefMiAcRv8JhM7m90p.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260601/nkEyZw9TcKRMHbTvSy6D591581101_00_00nkEyZw9TcKRMHbTvSy6D.jpg</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953530&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/j2jn8GpSpWpVPin1SKu2994953530_00_00j2jn8GpSpWpVPin1SKu2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,34 +4272,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618641&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/m3XnQVGNmWJfQCUZVnvy601618641_00_00m3XnQVGNmWJfQCUZVnvy.jpg</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,27 +4307,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=030086178&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260312/RhgSqjNOPs6aCmkpEpj2030086178_00_00RhgSqjNOPs6aCmkpEpj2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
@@ -4342,12 +4342,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>유한양행 프리바이오틱스 스틱 40포 20일분</t>
+          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4357,19 +4357,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651647&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/3lk29dAMMktUiVesbwgQ600651647_00_003lk29dAMMktUiVesbwgQ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 발효효소＆매실</t>
+          <t>대웅제약 루테인 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911031&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/AwS7hZ6EGxkGDWyKLCd8610911031_00_00AwS7hZ6EGxkGDWyKLCd8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
         </is>
       </c>
     </row>
@@ -4512,52 +4512,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -4569,52 +4569,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동화약품</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>닥터블릿</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -4626,52 +4626,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민미네랄 6정 6일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 마그네슘 30정 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[김우빈 PICK] 종근당건강 아임비타 멀티비타민 컴팩트 30정 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>동화 바이마그랩 마그네슘 테아닌 5포 5일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
           <t>대웅제약 루테인 30정 30일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>오브맘 스트레스,쉼 30일분</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>LG생활건강 이너뷰 레티놀 리포좀C 12포</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 레몬 비타C 500 10개입</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>유한양행 프리바이오틱스 스틱 40포 20일분</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[신혜선 PICK] 동국 마이팝 발효효소＆매실</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -4713,22 +4713,22 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[골라담기] 닥터언 매일루틴 이너헬스 8종 택 1</t>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터언</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6,300원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247070&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024707005ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,27 +4910,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>세노비스 밀크씨슬 120캡슐 선물세트 (4개월분)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>세노비스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000129053&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0012/A00000012905324ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,34 +5050,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[이준 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000237482&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023748213ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5085,27 +5085,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[골라담기] 여에스더 국민영양 12종 택1</t>
+          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>에스더포뮬러</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9,700원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000229402&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022940201ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563485ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GNM 유기농 동결건조 컬리 케일 100% 14포</t>
+          <t>[시나모롤/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 / 히카바이오틱스 위디어트 21포 산리오 콜라보</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GNM자연의품격</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6,950원</t>
+          <t>32,300원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244616&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000218073&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024461601ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021807367ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,27 +5155,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259818&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025981802ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265832ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 10포+1포 증정기획 (알파플러스, 오리지널)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5325,47 +5325,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -5382,47 +5382,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>닥터언</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
+          <t>세노비스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>멜라메이트</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>헬스헬퍼</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>에스더포뮬러</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>GNM자연의품격</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[골라담기] 닥터언 매일루틴 이너헬스 8종 택 1</t>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>세노비스 밀크씨슬 120캡슐 선물세트 (4개월분)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[이준 PICK] 헬스헬퍼 맥스컷 프로 크롬 60캡슐 (10일분)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[골라담기] 여에스더 국민영양 12종 택1</t>
+          <t>[8월 올영픽/서현PICK] 콜레올로지 PRO 600mg*30(+10)/60정 단품</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>GNM 유기농 동결건조 컬리 케일 100% 14포</t>
+          <t>[시나모롤/품절대란] 닥터아돌 카테킨 아세로라 칼시페롤 C D 60정 / 히카바이오틱스 위디어트 21포 산리오 콜라보</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>그레인온 파로효소 골드 캡슐레이션 30포 (1개월분)</t>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 10포+1포 증정기획 (알파플러스, 오리지널)</t>
         </is>
       </c>
     </row>
@@ -5496,47 +5496,47 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>6,300원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
+          <t>24,900원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>16,900원</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>11,900원</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>55,900원</t>
+          <t>18,900원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>9,700원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>6,950원</t>
+          <t>32,300원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -5629,7 +5629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,19 +5671,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5715,38 +5715,38 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -5755,20 +5755,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -5799,7 +5799,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5809,19 +5809,19 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,12 +5831,34 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
         <v>0</v>
       </c>
     </row>
